--- a/项目资料/FYF_BMS_MODBUS_TO_PC_RS485_Parameter_List_260609.xlsx
+++ b/项目资料/FYF_BMS_MODBUS_TO_PC_RS485_Parameter_List_260609.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="30" windowWidth="19440" windowHeight="11730"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="BMS - MODBUS" sheetId="3" r:id="rId1"/>
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'BMS - MODBUS'!$A$1:$I$34</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -53,6 +53,9 @@
     <t>Data type</t>
   </si>
   <si>
+    <t>0x0200</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -61,7 +64,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Total Number of Battery Stings(</t>
     </r>
@@ -70,7 +73,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>电池总串数</t>
@@ -80,7 +82,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
@@ -92,12 +94,15 @@
     <t>unsigned int</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0201</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage1(</t>
     </r>
@@ -106,7 +111,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -116,7 +120,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
@@ -131,12 +135,15 @@
     <t>1mV</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0202</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage2(</t>
     </r>
@@ -145,7 +152,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -155,18 +161,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0203</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage3(</t>
     </r>
@@ -175,7 +184,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -185,18 +193,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0204</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage4(</t>
     </r>
@@ -205,7 +216,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -215,18 +225,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0205</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage5(</t>
     </r>
@@ -235,7 +248,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -245,18 +257,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0206</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage6(</t>
     </r>
@@ -265,7 +280,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -275,18 +289,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0207</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage7(</t>
     </r>
@@ -295,7 +312,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -305,18 +321,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0208</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage8(</t>
     </r>
@@ -325,7 +344,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -335,18 +353,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0209</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage9(</t>
     </r>
@@ -355,7 +376,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -365,18 +385,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x020a</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage10(</t>
     </r>
@@ -385,7 +408,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -395,18 +417,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x020b</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage11(</t>
     </r>
@@ -415,7 +440,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -425,18 +449,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x020c</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage12(</t>
     </r>
@@ -445,7 +472,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -455,18 +481,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x020d</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage13(</t>
     </r>
@@ -475,7 +504,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -485,18 +513,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x020e</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage14(</t>
     </r>
@@ -505,7 +536,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -515,18 +545,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x020f</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage15(</t>
     </r>
@@ -535,7 +568,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -545,18 +577,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0210</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage16(</t>
     </r>
@@ -565,7 +600,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -575,18 +609,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0211</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage17(</t>
     </r>
@@ -595,7 +632,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -605,18 +641,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0212</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage18(</t>
     </r>
@@ -625,7 +664,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -635,18 +673,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0213</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage19(</t>
     </r>
@@ -655,7 +696,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -665,18 +705,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0214</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage20(</t>
     </r>
@@ -685,7 +728,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -695,18 +737,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0215</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage21(</t>
     </r>
@@ -715,7 +760,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -725,18 +769,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0216</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage22(</t>
     </r>
@@ -745,7 +792,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -755,18 +801,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0217</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage23(</t>
     </r>
@@ -775,7 +824,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -785,18 +833,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0218</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage24(</t>
     </r>
@@ -805,7 +856,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -815,18 +865,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0219</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage25(</t>
     </r>
@@ -835,7 +888,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -845,18 +897,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x021a</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage26(</t>
     </r>
@@ -865,7 +920,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -875,18 +929,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x021b</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage27(</t>
     </r>
@@ -895,7 +952,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -905,18 +961,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x021c</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage28(</t>
     </r>
@@ -925,7 +984,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -935,18 +993,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x021d</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage29(</t>
     </r>
@@ -955,7 +1016,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -965,18 +1025,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x021e</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage30(</t>
     </r>
@@ -985,7 +1048,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -995,18 +1057,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x021f</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage31(</t>
     </r>
@@ -1015,7 +1080,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -1025,18 +1089,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0220</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Single  Voltage32(</t>
     </r>
@@ -1045,7 +1112,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>单体电压</t>
@@ -1055,12 +1121,15 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
+    <t>0x0221</t>
+  </si>
+  <si>
     <t>Temprature1</t>
   </si>
   <si>
@@ -1075,7 +1144,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>0.1</t>
     </r>
@@ -1093,51 +1162,78 @@
     <t>signed int</t>
   </si>
   <si>
+    <t>0x0222</t>
+  </si>
+  <si>
     <t>Temprature2</t>
   </si>
   <si>
     <t xml:space="preserve">second channel temperature  </t>
   </si>
   <si>
+    <t>0x0223</t>
+  </si>
+  <si>
     <t>Temprature3</t>
   </si>
   <si>
     <t xml:space="preserve">third channel temperature  </t>
   </si>
   <si>
+    <t>0x0224</t>
+  </si>
+  <si>
     <t>Temprature4</t>
   </si>
   <si>
     <t xml:space="preserve">4th channel temperature </t>
   </si>
   <si>
+    <t>0x0225</t>
+  </si>
+  <si>
     <t>Temprature5</t>
   </si>
   <si>
     <t xml:space="preserve">5th channel temperature </t>
   </si>
   <si>
+    <t>0x0226</t>
+  </si>
+  <si>
     <t>Temprature6</t>
   </si>
   <si>
     <t xml:space="preserve">6th channel temperature </t>
   </si>
   <si>
+    <t>0x0227</t>
+  </si>
+  <si>
     <t>Temprature7</t>
   </si>
   <si>
     <t xml:space="preserve">7th channel temperature </t>
   </si>
   <si>
+    <t>0x0228</t>
+  </si>
+  <si>
     <t>Temprature8</t>
   </si>
   <si>
     <t xml:space="preserve">8th channel temperature </t>
   </si>
   <si>
+    <t>0x0229</t>
+  </si>
+  <si>
     <t>max Temprature</t>
   </si>
   <si>
+    <t>0x022a</t>
+  </si>
+  <si>
     <t>max Temprature No</t>
   </si>
   <si>
@@ -1147,33 +1243,54 @@
     <t>maximum temperature channel number</t>
   </si>
   <si>
+    <t>0x022b</t>
+  </si>
+  <si>
     <t>min Temprature</t>
   </si>
   <si>
+    <t>0x022c</t>
+  </si>
+  <si>
     <t>min Temprature No</t>
   </si>
   <si>
     <t>minimum temperature channel number</t>
   </si>
   <si>
+    <t>0x022d</t>
+  </si>
+  <si>
     <t>Single  max Voltage</t>
   </si>
   <si>
+    <t>0x022e</t>
+  </si>
+  <si>
     <t>Single  max Voltage No</t>
   </si>
   <si>
     <t>maximum single cell battery voltage channel number</t>
   </si>
   <si>
+    <t>0x022f</t>
+  </si>
+  <si>
     <t>Single  min Voltage</t>
   </si>
   <si>
+    <t>0x0230</t>
+  </si>
+  <si>
     <t>Single  min Voltage No</t>
   </si>
   <si>
     <t>minimum single cell battery voltage channel number</t>
   </si>
   <si>
+    <t>0x0231</t>
+  </si>
+  <si>
     <t>Total Voltage High Word</t>
   </si>
   <si>
@@ -1186,12 +1303,18 @@
     <t>unsigned long</t>
   </si>
   <si>
+    <t>0x0232</t>
+  </si>
+  <si>
     <t>Total Voltage  Low Word</t>
   </si>
   <si>
     <t>the lower word of total voltage of battery pack</t>
   </si>
   <si>
+    <t>0x0233</t>
+  </si>
+  <si>
     <t>Current High Word</t>
   </si>
   <si>
@@ -1204,12 +1327,18 @@
     <t>signed long</t>
   </si>
   <si>
+    <t>0x0234</t>
+  </si>
+  <si>
     <t>Current Low Word</t>
   </si>
   <si>
     <t>the lower word of total current of battery pack</t>
   </si>
   <si>
+    <t>0x0235</t>
+  </si>
+  <si>
     <t>R/W</t>
   </si>
   <si>
@@ -1218,7 +1347,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Designed Capacity High Word</t>
     </r>
@@ -1227,7 +1356,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（设计容量高字）</t>
@@ -1237,12 +1365,15 @@
     <t xml:space="preserve">           1mAH</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0236</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Designed Capacity Low Word</t>
     </r>
@@ -1251,13 +1382,15 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（设计容量低字）</t>
     </r>
   </si>
   <si>
+    <t>0x0237</t>
+  </si>
+  <si>
     <t xml:space="preserve">State of Capacity </t>
   </si>
   <si>
@@ -1272,7 +1405,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>1</t>
     </r>
@@ -1281,18 +1414,21 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Arial"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>‰</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+    <t>0x0238</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
       </rPr>
       <t>Battery Loop Times</t>
     </r>
@@ -1301,17 +1437,22 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（电池循环次数）</t>
     </r>
   </si>
   <si>
+    <t>0x0239</t>
+  </si>
+  <si>
     <t>Firmware Version</t>
   </si>
   <si>
     <t>eg,0x0102 means that current version is V1.2</t>
+  </si>
+  <si>
+    <t>0x023a</t>
   </si>
   <si>
     <t>Battery Sequence No</t>
@@ -1396,7 +1537,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Over Voltage Protect Value</t>
     </r>
@@ -1405,7 +1546,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（超压保护门限）</t>
@@ -1420,7 +1560,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Over Voltage Protect Delay Time</t>
     </r>
@@ -1429,7 +1569,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（超压保护延时）</t>
@@ -1450,7 +1589,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Over Voltage Restore Value</t>
     </r>
@@ -1459,7 +1598,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（超压保护恢复门限）</t>
@@ -1474,7 +1612,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Under Voltage Protect Value</t>
     </r>
@@ -1483,7 +1621,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（欠压保护门限）</t>
@@ -1498,7 +1635,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Under Voltage Protect Delay Time</t>
     </r>
@@ -1507,7 +1644,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（欠压保护延时）</t>
@@ -1522,7 +1658,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Under Voltage Restore Value</t>
     </r>
@@ -1531,7 +1667,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（欠压保护恢复门限</t>
@@ -1546,7 +1681,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Balance Start Voltage</t>
     </r>
@@ -1555,7 +1690,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（均衡开启电压）</t>
@@ -1570,7 +1704,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Balance Start Pressure Difference</t>
     </r>
@@ -1579,7 +1713,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（均衡开启压差）</t>
@@ -1594,7 +1727,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Discharge Overcurrent Level 1</t>
     </r>
@@ -1603,7 +1736,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（一级放电过流）</t>
@@ -1618,7 +1750,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Discharge Overcurrent Level 1 Delay</t>
     </r>
@@ -1627,7 +1759,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（一级放电过流延时）</t>
@@ -1642,7 +1773,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Discharge Overcurrent Level 2</t>
     </r>
@@ -1651,7 +1782,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（二级放电过流）</t>
@@ -1666,7 +1796,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Discharge Overcurrent Level 2 Delay</t>
     </r>
@@ -1675,7 +1805,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（二级放电过流延时）</t>
@@ -1690,7 +1819,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Charge Overcurrent value(</t>
     </r>
@@ -1699,7 +1828,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>充电过流门限</t>
@@ -1709,7 +1837,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
@@ -1723,7 +1851,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Charge Overcurrent Delay</t>
     </r>
@@ -1732,7 +1860,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（充电过流延时）</t>
@@ -1747,7 +1874,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Discharge Overtemperature Protect Temperature</t>
     </r>
@@ -1756,7 +1883,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（放电过温温度保护值）</t>
@@ -1771,7 +1897,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Discharge Overtemperature Restore Temperature</t>
     </r>
@@ -1780,7 +1906,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（放电过温温度恢复值）</t>
@@ -1795,7 +1920,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Discharge Undertemperature Protect Temperature</t>
     </r>
@@ -1804,7 +1929,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（放电低温温度保护值）</t>
@@ -1819,7 +1943,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Discharge Undertemperature Restore Temperature</t>
     </r>
@@ -1828,7 +1952,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（放电低温温度恢复值）</t>
@@ -1843,7 +1966,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Charge Overtemperature Protect Temperature</t>
     </r>
@@ -1852,7 +1975,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（充电过温温度保护值）</t>
@@ -1867,7 +1989,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Charge Overtemperature Restore Temperature</t>
     </r>
@@ -1876,7 +1998,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（充电过温温度恢复值）</t>
@@ -1891,7 +2012,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Charge Undertemperature Protect Temperature</t>
     </r>
@@ -1900,7 +2021,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（充电低温温度保护值）</t>
@@ -1915,7 +2035,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Charge Undertemperature Restore Temperature</t>
     </r>
@@ -1924,7 +2044,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（充电低温温度恢复值）</t>
@@ -1935,12 +2054,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
       <t>Remaining Capacity High Word</t>
     </r>
     <r>
@@ -1948,7 +2061,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（剩余容量高字）</t>
@@ -1963,7 +2075,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Remaining Capacity Low Word</t>
     </r>
@@ -1972,7 +2084,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（剩余容量低字）</t>
@@ -1987,7 +2098,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Function Parameter Set</t>
     </r>
@@ -1996,7 +2107,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（功能参数设置）</t>
@@ -2011,7 +2121,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Self Consumption Power(</t>
     </r>
@@ -2020,7 +2130,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>自耗电</t>
@@ -2030,7 +2139,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
@@ -2044,7 +2153,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Sleep Leakage Current</t>
     </r>
@@ -2053,7 +2162,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（休眠电流）</t>
@@ -2068,7 +2176,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>AFE2 Number of Battery Stings</t>
     </r>
@@ -2077,7 +2185,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（第</t>
@@ -2087,7 +2194,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>2</t>
     </r>
@@ -2096,7 +2203,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>模拟前端电池串数）</t>
@@ -2114,7 +2220,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>MOS Overtemperature Protect Temperature</t>
     </r>
@@ -2123,7 +2229,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（</t>
@@ -2133,7 +2238,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>MOS</t>
     </r>
@@ -2142,7 +2247,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>过温温度保护值）</t>
@@ -2157,7 +2261,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>MOS Overtemperature Restore Temperature</t>
     </r>
@@ -2166,7 +2270,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（</t>
@@ -2176,7 +2279,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>MOS</t>
     </r>
@@ -2185,7 +2288,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>过温温度恢复值）</t>
@@ -2239,7 +2341,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Exit Manul Mode(</t>
     </r>
@@ -2248,7 +2350,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>退出手动模式</t>
@@ -2258,7 +2359,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
@@ -2272,7 +2373,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Current Zeroing</t>
     </r>
@@ -2281,7 +2382,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（电流归零）</t>
@@ -2296,7 +2396,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Charging Correction</t>
     </r>
@@ -2305,7 +2405,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（充电校正）</t>
@@ -2323,7 +2422,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Discharging Correction</t>
     </r>
@@ -2332,7 +2431,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（放电校正）</t>
@@ -2350,7 +2448,7 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>Restore Factory Default</t>
     </r>
@@ -2359,7 +2457,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>（恢复出厂默认）</t>
@@ -2376,6 +2473,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>Total Number of NTC(</t>
     </r>
     <r>
@@ -2383,7 +2486,6 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>电池总串数</t>
@@ -2393,281 +2495,44 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
   </si>
   <si>
-    <t>0x0200</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0201</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0202</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0203</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0204</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0205</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0206</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0207</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0208</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0209</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x020a</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x020b</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x020c</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x020d</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x020e</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x020f</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0210</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0211</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0212</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0213</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0214</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0215</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0216</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0217</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0218</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0219</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x021a</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x021b</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x021c</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x021d</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x021e</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x021f</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0220</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0221</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0222</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0223</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0224</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0225</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0226</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0227</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0228</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0229</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x022a</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x022b</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x022c</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x022d</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x022e</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x022f</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0230</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0231</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0232</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0233</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0234</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0235</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0236</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0237</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0238</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x0239</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>0x023a</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <t>slave addr:0x97</t>
+  </si>
+  <si>
+    <t>read command(one or multi):0x03</t>
   </si>
   <si>
     <t>write one register command:0x06</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>write multi registers comand:0x10</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>CRC-16/MODBUS</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>read command(one or multi):0x03</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>slave addr:0x97</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>eg: 97 03 00 00 00 02 crcl crch     //read 2 regiters</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>eg: 97 06 00 01 04 d2 crcl crch     //write 0x04d2 into register 0x0001</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2686,7 +2551,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2715,20 +2580,164 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2736,15 +2745,8 @@
       <name val="SimSun"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2759,7 +2761,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39994506668294322"/>
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399945066682943"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2769,8 +2777,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2819,9 +3013,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2852,115 +3288,94 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2977,7 +3392,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -3221,12 +3636,11 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3257,11 +3671,11 @@
     <col min="24" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1">
-      <c r="A1" s="23" t="s">
+    <row r="1" s="1" customFormat="1" ht="12.75" spans="1:23">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="7"/>
       <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
@@ -3285,1795 +3699,1795 @@
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
       <c r="M1" s="10"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="11">
         <v>0</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>214</v>
+        <v>7</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="D2" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="E2" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="15"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="11">
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>13</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="16"/>
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="11">
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>216</v>
+        <v>17</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
       <c r="G4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="16"/>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="11">
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="15"/>
+      <c r="H5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="11">
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="11">
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>219</v>
+        <v>23</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>18</v>
+        <v>8</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="11">
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>220</v>
+        <v>25</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="11">
         <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>28</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:23">
       <c r="A10" s="11">
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>222</v>
+        <v>29</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="11">
         <v>9</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>223</v>
+        <v>31</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" s="11">
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>224</v>
+        <v>33</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>23</v>
+        <v>8</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="16"/>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" s="11">
         <v>11</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>24</v>
+        <v>8</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="16"/>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" s="11">
         <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>226</v>
+        <v>37</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>25</v>
+        <v>8</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="16"/>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" s="11">
         <v>13</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>227</v>
+        <v>39</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>26</v>
+        <v>8</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>40</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" s="11">
         <v>14</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>228</v>
+        <v>41</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>42</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="16"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="11">
         <v>15</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>229</v>
+        <v>43</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>44</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I17" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="16"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="11">
         <v>16</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>230</v>
+        <v>45</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>46</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="16"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="11">
         <v>17</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>231</v>
+        <v>47</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="11">
         <v>18</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>232</v>
+        <v>49</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="16"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="11">
         <v>19</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>233</v>
+        <v>51</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>32</v>
+        <v>8</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I21" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="16"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="11">
         <v>20</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>234</v>
+        <v>53</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>33</v>
+        <v>8</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>54</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I22" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="11">
         <v>21</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>235</v>
+        <v>55</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>34</v>
+        <v>8</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>56</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I23" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="16"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="11">
         <v>22</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>35</v>
+        <v>8</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I24" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="16"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="11">
         <v>23</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>237</v>
+        <v>59</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>36</v>
+        <v>8</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I25" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="16"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="11">
         <v>24</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>238</v>
+        <v>61</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>37</v>
+        <v>8</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I26" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="16"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="11">
         <v>25</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>239</v>
+        <v>63</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>64</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I27" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="16"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="11">
         <v>26</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>240</v>
+        <v>65</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>39</v>
+        <v>8</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I28" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="16"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="11">
         <v>27</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>241</v>
+        <v>67</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>40</v>
+        <v>8</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>68</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I29" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="16"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="11">
         <v>28</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>242</v>
+        <v>69</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>41</v>
+        <v>8</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>70</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I30" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="16"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="11">
         <v>29</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>243</v>
+        <v>71</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>42</v>
+        <v>8</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>72</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I31" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="16"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="11">
         <v>30</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>244</v>
+        <v>73</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>43</v>
+        <v>8</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I32" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="16"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="11">
         <v>31</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>44</v>
+        <v>8</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>76</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I33" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="16"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="11">
         <v>32</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>45</v>
+        <v>8</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>78</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I34" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="16"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="11">
         <v>33</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>247</v>
+        <v>79</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>46</v>
+        <v>8</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>80</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I35" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I35" s="16"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="11">
         <v>34</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>248</v>
+        <v>85</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>51</v>
+        <v>8</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G36" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I36" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I36" s="16"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="11">
         <v>35</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>249</v>
+        <v>88</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>53</v>
+        <v>8</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I37" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I37" s="16"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="11">
         <v>36</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>250</v>
+        <v>91</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>55</v>
+        <v>8</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I38" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I38" s="16"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="11">
         <v>37</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>251</v>
+        <v>94</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>57</v>
+        <v>8</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H39" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I39" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I39" s="16"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="11">
         <v>38</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>252</v>
+        <v>97</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>59</v>
+        <v>8</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I40" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I40" s="16"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="11">
         <v>39</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>61</v>
+        <v>8</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H41" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I41" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I41" s="16"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="11">
         <v>40</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>254</v>
+        <v>103</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>63</v>
+        <v>8</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G42" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I42" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I42" s="16"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="11">
         <v>41</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>255</v>
+        <v>106</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>65</v>
+        <v>8</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>107</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F43" s="12"/>
-      <c r="G43" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I43" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F43" s="13"/>
+      <c r="G43" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I43" s="16"/>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="11">
         <v>42</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>256</v>
+        <v>108</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>66</v>
+        <v>8</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="G44" s="17"/>
-      <c r="H44" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I44" s="15"/>
+        <v>110</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" s="18"/>
+      <c r="H44" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I44" s="16"/>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="11">
         <v>43</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>69</v>
+        <v>8</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>113</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H45" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I45" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F45" s="13"/>
+      <c r="G45" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I45" s="16"/>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="11">
         <v>44</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>258</v>
+        <v>114</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>70</v>
+        <v>8</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>115</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="G46" s="17"/>
-      <c r="H46" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I46" s="15"/>
+        <v>110</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G46" s="18"/>
+      <c r="H46" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" s="16"/>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="11">
         <v>45</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>259</v>
+        <v>117</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>72</v>
+        <v>8</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>118</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="F47" s="13"/>
       <c r="G47" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="16"/>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="11">
         <v>46</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>260</v>
+        <v>119</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>73</v>
+        <v>8</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>120</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G48" s="17"/>
-      <c r="H48" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I48" s="15"/>
+      <c r="F48" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G48" s="18"/>
+      <c r="H48" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="16"/>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="11">
         <v>47</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>261</v>
+        <v>122</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>75</v>
+        <v>8</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="F49" s="13"/>
       <c r="G49" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I49" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" s="16"/>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="11">
         <v>48</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>262</v>
+        <v>124</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>76</v>
+        <v>8</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>125</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="G50" s="17"/>
-      <c r="H50" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I50" s="15"/>
+      <c r="F50" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G50" s="18"/>
+      <c r="H50" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I50" s="16"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="11">
         <v>49</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>263</v>
+        <v>127</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>78</v>
+        <v>8</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>128</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G51" s="18" t="s">
-        <v>80</v>
+        <v>14</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>130</v>
       </c>
       <c r="H51" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="I51" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="I51" s="16"/>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="11">
         <v>50</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>264</v>
+        <v>132</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>82</v>
+        <v>8</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>133</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G52" s="19"/>
-      <c r="H52" s="22"/>
-      <c r="I52" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G52" s="22"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="16"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="11">
         <v>51</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>265</v>
+        <v>135</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>84</v>
+        <v>8</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>136</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="G53" s="18" t="s">
-        <v>86</v>
+        <v>14</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>138</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="I53" s="15"/>
+        <v>139</v>
+      </c>
+      <c r="I53" s="16"/>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="11">
         <v>52</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>266</v>
+        <v>140</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>88</v>
+        <v>8</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>141</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G54" s="19"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G54" s="22"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="16"/>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="11">
         <v>53</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>267</v>
+        <v>143</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>91</v>
+        <v>144</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>145</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="18" t="s">
-        <v>92</v>
+        <v>14</v>
+      </c>
+      <c r="F55" s="13"/>
+      <c r="G55" s="20" t="s">
+        <v>146</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="I55" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="I55" s="16"/>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="11">
         <v>54</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>268</v>
+        <v>147</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>93</v>
+        <v>144</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>148</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="12"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F56" s="13"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="16"/>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="11">
         <v>55</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>269</v>
+        <v>149</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>94</v>
+        <v>8</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>150</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G57" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I57" s="15"/>
+        <v>151</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="G57" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="H57" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="16"/>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="11">
         <v>56</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>270</v>
+        <v>154</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>98</v>
+        <v>8</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>155</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="12"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I58" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F58" s="13"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="16"/>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="11">
         <v>57</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>271</v>
+        <v>156</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>99</v>
+        <v>8</v>
+      </c>
+      <c r="D59" s="17" t="s">
+        <v>157</v>
       </c>
       <c r="E59" s="11"/>
-      <c r="F59" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G59" s="20"/>
-      <c r="H59" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I59" s="15"/>
+      <c r="F59" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G59" s="24"/>
+      <c r="H59" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I59" s="16"/>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="11">
         <v>58</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>272</v>
+        <v>159</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>101</v>
+        <v>8</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>160</v>
       </c>
       <c r="E60" s="11"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I60" s="15"/>
-    </row>
-    <row r="61" spans="1:9" ht="134.1" customHeight="1">
+      <c r="F60" s="13"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I60" s="16"/>
+    </row>
+    <row r="61" ht="134.1" customHeight="1" spans="1:9">
       <c r="A61" s="11">
         <v>59</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>103</v>
+        <v>8</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="G61" s="17"/>
-      <c r="H61" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I61" s="15"/>
+        <v>164</v>
+      </c>
+      <c r="G61" s="18"/>
+      <c r="H61" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I61" s="16"/>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="11">
         <v>60</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>107</v>
+        <v>8</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>166</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F62" s="12"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I62" s="15"/>
-    </row>
-    <row r="63" spans="1:9" ht="24">
+        <v>167</v>
+      </c>
+      <c r="F62" s="13"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I62" s="16"/>
+    </row>
+    <row r="63" ht="24" spans="1:9">
       <c r="A63" s="11">
         <v>61</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>110</v>
+        <v>8</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>169</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F63" s="12"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I63" s="15"/>
+        <v>170</v>
+      </c>
+      <c r="F63" s="13"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I63" s="16"/>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="11">
         <v>62</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>113</v>
+        <v>8</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>172</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F64" s="12"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I64" s="15"/>
+        <v>167</v>
+      </c>
+      <c r="F64" s="13"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" s="16"/>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="11">
         <v>63</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>115</v>
+        <v>8</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>174</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="F65" s="12"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I65" s="15"/>
+        <v>175</v>
+      </c>
+      <c r="F65" s="13"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I65" s="16"/>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="11">
         <v>64</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>118</v>
+        <v>8</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="F66" s="12"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I66" s="15"/>
+        <v>175</v>
+      </c>
+      <c r="F66" s="13"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I66" s="16"/>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="11">
         <v>65</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>120</v>
+        <v>8</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F67" s="12"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I67" s="15"/>
+        <v>180</v>
+      </c>
+      <c r="F67" s="13"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" s="16"/>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="11">
         <v>66</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>123</v>
+        <v>144</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>182</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="F68" s="13"/>
       <c r="G68" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I68" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I68" s="16"/>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="11">
         <v>67</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>124</v>
+        <v>183</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>125</v>
+        <v>144</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>184</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F69" s="12"/>
-      <c r="G69" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H69" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I69" s="15"/>
+        <v>185</v>
+      </c>
+      <c r="F69" s="13"/>
+      <c r="G69" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="H69" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I69" s="16"/>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="11">
         <v>68</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>129</v>
+        <v>144</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>188</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="F70" s="13"/>
       <c r="G70" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" s="14" t="s">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5081,934 +5495,934 @@
         <v>69</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>131</v>
+        <v>144</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F71" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="F71" s="13"/>
       <c r="G71" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I71" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I71" s="16"/>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="11">
         <v>70</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>133</v>
+        <v>144</v>
+      </c>
+      <c r="D72" s="17" t="s">
+        <v>192</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F72" s="12"/>
-      <c r="G72" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H72" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I72" s="15"/>
+        <v>185</v>
+      </c>
+      <c r="F72" s="13"/>
+      <c r="G72" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I72" s="16"/>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="11">
         <v>71</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
+      </c>
+      <c r="D73" s="17" t="s">
+        <v>194</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="F73" s="13"/>
       <c r="G73" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H73" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I73" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I73" s="16"/>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="11">
         <v>72</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D74" s="16" t="s">
-        <v>137</v>
+        <v>144</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="F74" s="13"/>
       <c r="G74" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I74" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H74" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I74" s="16"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="11">
         <v>73</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="12"/>
+        <v>14</v>
+      </c>
+      <c r="F75" s="13"/>
       <c r="G75" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H75" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I75" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I75" s="16"/>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="11">
         <v>74</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>141</v>
+        <v>144</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>200</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" s="12"/>
-      <c r="G76" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H76" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I76" s="15"/>
-    </row>
-    <row r="77" spans="1:9" ht="14.1" customHeight="1">
+        <v>14</v>
+      </c>
+      <c r="F76" s="13"/>
+      <c r="G76" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I76" s="16"/>
+    </row>
+    <row r="77" ht="14.1" customHeight="1" spans="1:9">
       <c r="A77" s="11">
         <v>75</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>202</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F77" s="12"/>
-      <c r="G77" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H77" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I77" s="15"/>
+        <v>185</v>
+      </c>
+      <c r="F77" s="13"/>
+      <c r="G77" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="H77" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I77" s="16"/>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="11">
         <v>76</v>
       </c>
       <c r="B78" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C78" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C78" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D78" s="16" t="s">
-        <v>145</v>
+      <c r="D78" s="17" t="s">
+        <v>204</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="12"/>
-      <c r="G78" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H78" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I78" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F78" s="13"/>
+      <c r="G78" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H78" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I78" s="16"/>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="11">
         <v>77</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D79" s="16" t="s">
-        <v>147</v>
+        <v>144</v>
+      </c>
+      <c r="D79" s="17" t="s">
+        <v>206</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F79" s="12"/>
-      <c r="G79" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H79" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I79" s="15"/>
+        <v>185</v>
+      </c>
+      <c r="F79" s="13"/>
+      <c r="G79" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="H79" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I79" s="16"/>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="11">
         <v>78</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>148</v>
+        <v>207</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>149</v>
+        <v>144</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>208</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F80" s="12"/>
-      <c r="G80" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H80" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I80" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F80" s="13"/>
+      <c r="G80" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H80" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I80" s="16"/>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="11">
         <v>79</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D81" s="16" t="s">
-        <v>151</v>
+        <v>144</v>
+      </c>
+      <c r="D81" s="17" t="s">
+        <v>210</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F81" s="12"/>
-      <c r="G81" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="H81" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I81" s="15"/>
+        <v>185</v>
+      </c>
+      <c r="F81" s="13"/>
+      <c r="G81" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I81" s="16"/>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="11">
         <v>80</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D82" s="16" t="s">
-        <v>153</v>
+        <v>144</v>
+      </c>
+      <c r="D82" s="17" t="s">
+        <v>212</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F82" s="12"/>
-      <c r="G82" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H82" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I82" s="15"/>
-    </row>
-    <row r="83" spans="1:9" ht="15.95" customHeight="1">
+        <v>81</v>
+      </c>
+      <c r="F82" s="13"/>
+      <c r="G82" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H82" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I82" s="16"/>
+    </row>
+    <row r="83" ht="15.95" customHeight="1" spans="1:9">
       <c r="A83" s="11">
         <v>81</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>155</v>
+        <v>144</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>214</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F83" s="12"/>
-      <c r="G83" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H83" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I83" s="15"/>
-    </row>
-    <row r="84" spans="1:9" ht="14.1" customHeight="1">
+        <v>81</v>
+      </c>
+      <c r="F83" s="13"/>
+      <c r="G83" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H83" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I83" s="16"/>
+    </row>
+    <row r="84" ht="14.1" customHeight="1" spans="1:9">
       <c r="A84" s="11">
         <v>82</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D84" s="16" t="s">
-        <v>157</v>
+        <v>144</v>
+      </c>
+      <c r="D84" s="17" t="s">
+        <v>216</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F84" s="12"/>
-      <c r="G84" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H84" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I84" s="15"/>
-    </row>
-    <row r="85" spans="1:9" ht="12.95" customHeight="1">
+        <v>81</v>
+      </c>
+      <c r="F84" s="13"/>
+      <c r="G84" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H84" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I84" s="16"/>
+    </row>
+    <row r="85" ht="12.95" customHeight="1" spans="1:9">
       <c r="A85" s="11">
         <v>83</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D85" s="16" t="s">
-        <v>159</v>
+        <v>144</v>
+      </c>
+      <c r="D85" s="17" t="s">
+        <v>218</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F85" s="12"/>
-      <c r="G85" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H85" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I85" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F85" s="13"/>
+      <c r="G85" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I85" s="16"/>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="11">
         <v>84</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D86" s="16" t="s">
-        <v>161</v>
+        <v>144</v>
+      </c>
+      <c r="D86" s="17" t="s">
+        <v>220</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F86" s="12"/>
-      <c r="G86" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H86" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I86" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F86" s="13"/>
+      <c r="G86" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H86" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I86" s="16"/>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="11">
         <v>85</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D87" s="16" t="s">
-        <v>163</v>
+        <v>144</v>
+      </c>
+      <c r="D87" s="17" t="s">
+        <v>222</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F87" s="12"/>
-      <c r="G87" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H87" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I87" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F87" s="13"/>
+      <c r="G87" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I87" s="16"/>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="11">
         <v>86</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D88" s="16" t="s">
-        <v>165</v>
+        <v>144</v>
+      </c>
+      <c r="D88" s="17" t="s">
+        <v>224</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F88" s="12"/>
-      <c r="G88" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H88" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I88" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F88" s="13"/>
+      <c r="G88" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H88" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I88" s="16"/>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="11">
         <v>87</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D89" s="16" t="s">
-        <v>167</v>
+        <v>144</v>
+      </c>
+      <c r="D89" s="17" t="s">
+        <v>226</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F89" s="12"/>
-      <c r="G89" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H89" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I89" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F89" s="13"/>
+      <c r="G89" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H89" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I89" s="16"/>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="11">
         <v>88</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>168</v>
+        <v>227</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D90" s="16" t="s">
-        <v>169</v>
+        <v>144</v>
+      </c>
+      <c r="D90" s="17" t="s">
+        <v>228</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" s="12"/>
-      <c r="G90" s="18" t="s">
-        <v>92</v>
+        <v>14</v>
+      </c>
+      <c r="F90" s="13"/>
+      <c r="G90" s="20" t="s">
+        <v>146</v>
       </c>
       <c r="H90" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="I90" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="I90" s="16"/>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="11">
         <v>89</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D91" s="16" t="s">
-        <v>171</v>
+        <v>144</v>
+      </c>
+      <c r="D91" s="17" t="s">
+        <v>230</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F91" s="12"/>
-      <c r="G91" s="19"/>
-      <c r="H91" s="22"/>
-      <c r="I91" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F91" s="13"/>
+      <c r="G91" s="22"/>
+      <c r="H91" s="23"/>
+      <c r="I91" s="16"/>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="11">
         <v>90</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D92" s="16" t="s">
-        <v>173</v>
+        <v>144</v>
+      </c>
+      <c r="D92" s="17" t="s">
+        <v>232</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" s="12"/>
-      <c r="G92" s="17"/>
-      <c r="H92" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I92" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F92" s="13"/>
+      <c r="G92" s="18"/>
+      <c r="H92" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I92" s="16"/>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="11">
         <v>91</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D93" s="16" t="s">
-        <v>175</v>
+        <v>144</v>
+      </c>
+      <c r="D93" s="17" t="s">
+        <v>234</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" s="12"/>
-      <c r="G93" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H93" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I93" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F93" s="13"/>
+      <c r="G93" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H93" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I93" s="16"/>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="11">
         <v>92</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>176</v>
+        <v>235</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D94" s="16" t="s">
-        <v>177</v>
+        <v>144</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>236</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" s="12"/>
-      <c r="G94" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H94" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I94" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F94" s="13"/>
+      <c r="G94" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I94" s="16"/>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="11">
         <v>93</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D95" s="16" t="s">
-        <v>179</v>
+        <v>144</v>
+      </c>
+      <c r="D95" s="19" t="s">
+        <v>238</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="F95" s="12"/>
-      <c r="G95" s="17"/>
-      <c r="H95" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I95" s="15"/>
+        <v>239</v>
+      </c>
+      <c r="F95" s="13"/>
+      <c r="G95" s="18"/>
+      <c r="H95" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I95" s="16"/>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="11">
         <v>94</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D96" s="16" t="s">
-        <v>182</v>
+        <v>144</v>
+      </c>
+      <c r="D96" s="17" t="s">
+        <v>241</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F96" s="12"/>
-      <c r="G96" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H96" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I96" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F96" s="13"/>
+      <c r="G96" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H96" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I96" s="16"/>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="11">
         <v>95</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D97" s="16" t="s">
-        <v>184</v>
+        <v>144</v>
+      </c>
+      <c r="D97" s="17" t="s">
+        <v>243</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F97" s="12"/>
-      <c r="G97" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="H97" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I97" s="15"/>
+        <v>81</v>
+      </c>
+      <c r="F97" s="13"/>
+      <c r="G97" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H97" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I97" s="16"/>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="11">
         <v>96</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D98" s="16" t="s">
-        <v>187</v>
+        <v>245</v>
+      </c>
+      <c r="D98" s="17" t="s">
+        <v>246</v>
       </c>
       <c r="E98" s="11">
         <v>1</v>
       </c>
-      <c r="F98" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="G98" s="17"/>
-      <c r="H98" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I98" s="15"/>
+      <c r="F98" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G98" s="18"/>
+      <c r="H98" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I98" s="16"/>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="11">
         <v>97</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D99" s="16" t="s">
-        <v>190</v>
+        <v>245</v>
+      </c>
+      <c r="D99" s="17" t="s">
+        <v>249</v>
       </c>
       <c r="E99" s="11">
         <v>1</v>
       </c>
-      <c r="F99" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="G99" s="17"/>
-      <c r="H99" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I99" s="15"/>
+      <c r="F99" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="G99" s="18"/>
+      <c r="H99" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I99" s="16"/>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="11">
         <v>98</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>193</v>
+        <v>245</v>
+      </c>
+      <c r="D100" s="17" t="s">
+        <v>252</v>
       </c>
       <c r="E100" s="11">
         <v>1</v>
       </c>
-      <c r="F100" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="G100" s="17"/>
-      <c r="H100" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I100" s="15"/>
+      <c r="F100" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="G100" s="18"/>
+      <c r="H100" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I100" s="16"/>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="11">
         <v>99</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>195</v>
+        <v>254</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D101" s="16" t="s">
-        <v>196</v>
+        <v>245</v>
+      </c>
+      <c r="D101" s="17" t="s">
+        <v>255</v>
       </c>
       <c r="E101" s="11">
         <v>1</v>
       </c>
-      <c r="F101" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="G101" s="17"/>
-      <c r="H101" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I101" s="15"/>
+      <c r="F101" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="G101" s="18"/>
+      <c r="H101" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I101" s="16"/>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="11">
         <v>100</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D102" s="16" t="s">
-        <v>199</v>
+        <v>245</v>
+      </c>
+      <c r="D102" s="17" t="s">
+        <v>258</v>
       </c>
       <c r="E102" s="11">
         <v>1</v>
       </c>
-      <c r="F102" s="12"/>
-      <c r="G102" s="17"/>
-      <c r="H102" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I102" s="15"/>
+      <c r="F102" s="13"/>
+      <c r="G102" s="18"/>
+      <c r="H102" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I102" s="16"/>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="11">
         <v>101</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D103" s="16" t="s">
-        <v>201</v>
+        <v>245</v>
+      </c>
+      <c r="D103" s="17" t="s">
+        <v>260</v>
       </c>
       <c r="E103" s="11">
         <v>1</v>
       </c>
-      <c r="F103" s="12"/>
-      <c r="G103" s="17"/>
-      <c r="H103" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I103" s="15"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="18"/>
+      <c r="H103" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I103" s="16"/>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="11">
         <v>102</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D104" s="16" t="s">
-        <v>203</v>
+        <v>245</v>
+      </c>
+      <c r="D104" s="17" t="s">
+        <v>262</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="G104" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H104" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I104" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F104" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="G104" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H104" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I104" s="16"/>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="11">
         <v>103</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>205</v>
+        <v>264</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D105" s="16" t="s">
-        <v>206</v>
+        <v>245</v>
+      </c>
+      <c r="D105" s="17" t="s">
+        <v>265</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F105" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="G105" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H105" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I105" s="15"/>
+        <v>14</v>
+      </c>
+      <c r="F105" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="G105" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H105" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I105" s="16"/>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="11">
         <v>104</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D106" s="16" t="s">
-        <v>209</v>
+        <v>245</v>
+      </c>
+      <c r="D106" s="17" t="s">
+        <v>268</v>
       </c>
       <c r="E106" s="11">
         <v>1</v>
       </c>
-      <c r="F106" s="12"/>
-      <c r="G106" s="18"/>
-      <c r="H106" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I106" s="15"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="20"/>
+      <c r="H106" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I106" s="16"/>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="11">
         <v>105</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D107" s="16" t="s">
-        <v>211</v>
+        <v>8</v>
+      </c>
+      <c r="D107" s="17" t="s">
+        <v>270</v>
       </c>
       <c r="E107" s="11"/>
-      <c r="F107" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G107" s="17"/>
-      <c r="H107" s="14"/>
-      <c r="I107" s="15"/>
+      <c r="F107" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G107" s="18"/>
+      <c r="H107" s="15"/>
+      <c r="I107" s="16"/>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="11">
         <v>0</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F108" s="12"/>
-      <c r="G108" s="13"/>
-      <c r="H108" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I108" s="15"/>
+        <v>110</v>
+      </c>
+      <c r="F108" s="13"/>
+      <c r="G108" s="14"/>
+      <c r="H108" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I108" s="16"/>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="11">
@@ -6016,12 +6430,12 @@
       </c>
       <c r="B109" s="11"/>
       <c r="C109" s="11"/>
-      <c r="D109" s="16"/>
+      <c r="D109" s="19"/>
       <c r="E109" s="11"/>
-      <c r="F109" s="12"/>
-      <c r="G109" s="17"/>
-      <c r="H109" s="14"/>
-      <c r="I109" s="15"/>
+      <c r="F109" s="13"/>
+      <c r="G109" s="18"/>
+      <c r="H109" s="15"/>
+      <c r="I109" s="16"/>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="11">
@@ -6029,12 +6443,12 @@
       </c>
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
-      <c r="D110" s="16"/>
+      <c r="D110" s="19"/>
       <c r="E110" s="11"/>
-      <c r="F110" s="12"/>
-      <c r="G110" s="17"/>
-      <c r="H110" s="14"/>
-      <c r="I110" s="15"/>
+      <c r="F110" s="13"/>
+      <c r="G110" s="18"/>
+      <c r="H110" s="15"/>
+      <c r="I110" s="16"/>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="11">
@@ -6042,12 +6456,12 @@
       </c>
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
-      <c r="D111" s="16"/>
+      <c r="D111" s="19"/>
       <c r="E111" s="11"/>
-      <c r="F111" s="12"/>
-      <c r="G111" s="17"/>
-      <c r="H111" s="14"/>
-      <c r="I111" s="15"/>
+      <c r="F111" s="13"/>
+      <c r="G111" s="18"/>
+      <c r="H111" s="15"/>
+      <c r="I111" s="16"/>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="11">
@@ -6055,12 +6469,12 @@
       </c>
       <c r="B112" s="11"/>
       <c r="C112" s="11"/>
-      <c r="D112" s="16"/>
+      <c r="D112" s="19"/>
       <c r="E112" s="11"/>
-      <c r="F112" s="12"/>
-      <c r="G112" s="17"/>
-      <c r="H112" s="14"/>
-      <c r="I112" s="15"/>
+      <c r="F112" s="13"/>
+      <c r="G112" s="18"/>
+      <c r="H112" s="15"/>
+      <c r="I112" s="16"/>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="11">
@@ -6068,12 +6482,12 @@
       </c>
       <c r="B113" s="11"/>
       <c r="C113" s="11"/>
-      <c r="D113" s="16"/>
+      <c r="D113" s="19"/>
       <c r="E113" s="11"/>
-      <c r="F113" s="12"/>
-      <c r="G113" s="17"/>
-      <c r="H113" s="14"/>
-      <c r="I113" s="15"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="15"/>
+      <c r="I113" s="16"/>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="11">
@@ -6081,12 +6495,12 @@
       </c>
       <c r="B114" s="11"/>
       <c r="C114" s="11"/>
-      <c r="D114" s="16"/>
+      <c r="D114" s="19"/>
       <c r="E114" s="11"/>
-      <c r="F114" s="12"/>
-      <c r="G114" s="17"/>
-      <c r="H114" s="14"/>
-      <c r="I114" s="15"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="15"/>
+      <c r="I114" s="16"/>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="11">
@@ -6094,12 +6508,12 @@
       </c>
       <c r="B115" s="11"/>
       <c r="C115" s="11"/>
-      <c r="D115" s="16"/>
+      <c r="D115" s="19"/>
       <c r="E115" s="11"/>
-      <c r="F115" s="12"/>
-      <c r="G115" s="17"/>
-      <c r="H115" s="14"/>
-      <c r="I115" s="15"/>
+      <c r="F115" s="13"/>
+      <c r="G115" s="18"/>
+      <c r="H115" s="15"/>
+      <c r="I115" s="16"/>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="11">
@@ -6107,12 +6521,12 @@
       </c>
       <c r="B116" s="11"/>
       <c r="C116" s="11"/>
-      <c r="D116" s="16"/>
+      <c r="D116" s="19"/>
       <c r="E116" s="11"/>
-      <c r="F116" s="12"/>
-      <c r="G116" s="17"/>
-      <c r="H116" s="14"/>
-      <c r="I116" s="15"/>
+      <c r="F116" s="13"/>
+      <c r="G116" s="18"/>
+      <c r="H116" s="15"/>
+      <c r="I116" s="16"/>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="11">
@@ -6120,12 +6534,12 @@
       </c>
       <c r="B117" s="11"/>
       <c r="C117" s="11"/>
-      <c r="D117" s="16"/>
+      <c r="D117" s="19"/>
       <c r="E117" s="11"/>
-      <c r="F117" s="12"/>
-      <c r="G117" s="17"/>
-      <c r="H117" s="14"/>
-      <c r="I117" s="15"/>
+      <c r="F117" s="13"/>
+      <c r="G117" s="18"/>
+      <c r="H117" s="15"/>
+      <c r="I117" s="16"/>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="11">
@@ -6133,12 +6547,12 @@
       </c>
       <c r="B118" s="11"/>
       <c r="C118" s="11"/>
-      <c r="D118" s="16"/>
+      <c r="D118" s="19"/>
       <c r="E118" s="11"/>
-      <c r="F118" s="12"/>
-      <c r="G118" s="17"/>
-      <c r="H118" s="14"/>
-      <c r="I118" s="15"/>
+      <c r="F118" s="13"/>
+      <c r="G118" s="18"/>
+      <c r="H118" s="15"/>
+      <c r="I118" s="16"/>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="11">
@@ -6146,12 +6560,12 @@
       </c>
       <c r="B119" s="11"/>
       <c r="C119" s="11"/>
-      <c r="D119" s="16"/>
+      <c r="D119" s="19"/>
       <c r="E119" s="11"/>
-      <c r="F119" s="12"/>
-      <c r="G119" s="17"/>
-      <c r="H119" s="14"/>
-      <c r="I119" s="15"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="18"/>
+      <c r="H119" s="15"/>
+      <c r="I119" s="16"/>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="11">
@@ -6159,12 +6573,12 @@
       </c>
       <c r="B120" s="11"/>
       <c r="C120" s="11"/>
-      <c r="D120" s="16"/>
+      <c r="D120" s="19"/>
       <c r="E120" s="11"/>
-      <c r="F120" s="12"/>
-      <c r="G120" s="17"/>
-      <c r="H120" s="14"/>
-      <c r="I120" s="15"/>
+      <c r="F120" s="13"/>
+      <c r="G120" s="18"/>
+      <c r="H120" s="15"/>
+      <c r="I120" s="16"/>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="11">
@@ -6172,12 +6586,12 @@
       </c>
       <c r="B121" s="11"/>
       <c r="C121" s="11"/>
-      <c r="D121" s="16"/>
+      <c r="D121" s="19"/>
       <c r="E121" s="11"/>
-      <c r="F121" s="12"/>
-      <c r="G121" s="17"/>
-      <c r="H121" s="14"/>
-      <c r="I121" s="15"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="18"/>
+      <c r="H121" s="15"/>
+      <c r="I121" s="16"/>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="11">
@@ -6185,36 +6599,36 @@
       </c>
       <c r="B122" s="11"/>
       <c r="C122" s="11"/>
-      <c r="D122" s="16"/>
+      <c r="D122" s="19"/>
       <c r="E122" s="11"/>
-      <c r="F122" s="12"/>
-      <c r="G122" s="17"/>
-      <c r="H122" s="14"/>
-      <c r="I122" s="15"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="18"/>
+      <c r="H122" s="15"/>
+      <c r="I122" s="16"/>
     </row>
     <row r="123" spans="1:9">
       <c r="D123" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="D124" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="D125" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="D126" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="D127" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="129" spans="4:4">
@@ -6229,15 +6643,15 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="H90:H91"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="N1:W1"/>
     <mergeCell ref="H51:H52"/>
     <mergeCell ref="H53:H54"/>
     <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H90:H91"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>